--- a/feedback_forms/050_evidence_summary_survey--feedback_forms.xlsx
+++ b/feedback_forms/050_evidence_summary_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>general_info</t>
+          <t>general_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>general_info</t>
+          <t>General Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>evidence_selection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>Select Relevant Evidence or Findings</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>summary_statement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>Summary of Findings or Evidence</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>impact_statement</t>
+          <t>Impact Statement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>evidence_statement</t>
+          <t>Detailed Description of Evidence or Findings</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reference_statement</t>
+          <t>Reference or Citation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other_statement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,19 +755,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_tool_description</t>
+          <t>participant_info_general</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assigned_tool_description</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Provide a brief description of the tool assigned to this participant</t>
-        </is>
-      </c>
+          <t>Participant Information</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -782,338 +778,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_info</t>
+          <t>participant_info_tool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_info</t>
+          <t>Participant Info Tool</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>participant_info_form_id</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>participant_info_form_id</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_info_assigned_tool</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>participant_info_assigned_tool</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>participant_info_email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>participant_info_email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_info_phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>participant_info_phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_info_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>participant_info_name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_info_job_title</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>participant_info_job_title</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_info_department</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>participant_info_department</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_info_institution</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>participant_info_institution</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_info_job_title_other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>participant_info_job_title</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_info_department_other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>participant_info_department</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_info_institution_other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>participant_info_institution</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_info_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>participant_info_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_info_date_time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>participant_info_date_time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_info_date_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>participant_info_date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1130,10 +804,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1158,7 +832,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>evidence_choices</t>
+          <t>evidence_selection_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1175,7 +849,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>evidence_choices</t>
+          <t>evidence_selection_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1192,7 +866,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>evidence_choices</t>
+          <t>evidence_selection_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1235,40 +909,6 @@
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>participant_info_assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>participant_info_assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>other</t>
         </is>
